--- a/DesignData/Luban/Datas/Enums.xlsx
+++ b/DesignData/Luban/Datas/Enums.xlsx
@@ -1259,17 +1259,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>remark</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>member_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>value</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>remark</t>
         </is>
       </c>
     </row>
@@ -1281,10 +1281,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>覆盖打开</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Overlay</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0</v>
       </c>
     </row>
@@ -1296,10 +1301,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>入栈打开</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Push</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
     </row>
@@ -1311,10 +1321,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>替换当前界面</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Replace</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2</v>
       </c>
     </row>
@@ -1326,10 +1341,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>返回来源</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>ReturnToSource</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0</v>
       </c>
     </row>
@@ -1341,10 +1361,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>继承来源</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>InheritSource</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1</v>
       </c>
     </row>
@@ -1356,10 +1381,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>显式指定</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Explicit</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>2</v>
       </c>
     </row>
@@ -1371,10 +1401,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>禁用返回</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Disabled</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>3</v>
       </c>
     </row>

--- a/DesignData/Luban/Datas/Enums.xlsx
+++ b/DesignData/Luban/Datas/Enums.xlsx
@@ -1313,26 +1313,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EUIJumpMode</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>替换当前界面</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Replace</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
